--- a/feedback_surveys/024_coupling_expansion_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/024_coupling_expansion_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied',_'value':_1}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied', 'value': 1}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied',_'value':_2}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied', 'value': 2}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_4}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': 4}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_5}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': 5}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely',_'value':_1}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely', 'value': 1}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely',_'value':_2}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely', 'value': 2}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -876,29 +876,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely',_'value':_4}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely', 'value': 4}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely',_'value':_5}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely', 'value': 5}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_1}</t>
+          <t>somewhat_poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor', 'value': 1}</t>
+          <t>Somewhat Poor</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_poor',_'value':_2}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Poor', 'value': 2}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Somewhat Good</t>
         </is>
       </c>
     </row>
@@ -961,29 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_good',_'value':_4}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Good', 'value': 4}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>question3_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'very_good',_'value':_5}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Very Good', 'value': 5}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
